--- a/data/Quarto_YAMLs.xlsx
+++ b/data/Quarto_YAMLs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R入門\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB83441D-0C44-45C1-AE7B-C77890CD7BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C7D3D5-7F5F-4503-B417-857B222B555B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{BD8A1D6D-0391-4D96-8986-F577B78F0501}"/>
   </bookViews>

--- a/data/Quarto_YAMLs.xlsx
+++ b/data/Quarto_YAMLs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R入門\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C7D3D5-7F5F-4503-B417-857B222B555B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A749EB1A-C386-4946-AE8B-B8731214CE64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{BD8A1D6D-0391-4D96-8986-F577B78F0501}"/>
+    <workbookView xWindow="-19230" yWindow="2880" windowWidth="20775" windowHeight="11835" activeTab="7" xr2:uid="{BD8A1D6D-0391-4D96-8986-F577B78F0501}"/>
   </bookViews>
   <sheets>
     <sheet name="format" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="navbar" sheetId="5" r:id="rId5"/>
     <sheet name="sidebar" sheetId="6" r:id="rId6"/>
     <sheet name="code" sheetId="7" r:id="rId7"/>
+    <sheet name="listing" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="188">
   <si>
     <t>YAMLでのformat設定</t>
     <rPh sb="12" eb="14">
@@ -168,19 +169,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>別設定に従う</t>
-    <rPh sb="0" eb="1">
-      <t>ベツ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>シタガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>設定項目の意味</t>
     <rPh sb="0" eb="4">
       <t>セッテイコウモク</t>
@@ -1115,6 +1103,173 @@
     <t>コードハイライトを適用するか</t>
     <rPh sb="9" eb="11">
       <t>テキヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>論文（HTML）</t>
+    <rPh sb="0" eb="2">
+      <t>ロンブン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>confluence</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>confluence（Wiki的な文書、HTML）</t>
+    <rPh sb="15" eb="16">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ブンショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>default</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>デフォルト（HTML）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sort</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>max-items</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>page-size</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>feed</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>grid-columns</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>table-hover</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>`default`、`table`、`grid`、`custom`</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Listingの表示のタイプ</t>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サブフォルダ名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Listingに表示する記事を保存したサブフォルダ</t>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>`date asc`、`date desc`</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Listingの表示順</t>
+    <rPh sb="8" eb="11">
+      <t>ヒョウジジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Listingに表示する記事の最大数</t>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="15" eb="18">
+      <t>サイダイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1ページに表示する記事の数</t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>カズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>true/false</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RSSフィードを有効にする</t>
+    <rPh sb="8" eb="10">
+      <t>ユウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>表示する列の数</t>
+    <rPh sb="0" eb="2">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>レツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>カズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Postをマウスで選択するとハイライトされる</t>
+    <rPh sb="9" eb="11">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>categories</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カテゴリを表示するかどうか</t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1603,7 +1758,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B551F96-E27C-45FC-A060-6E9BFFD40BCC}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="20.75" bestFit="1" customWidth="1"/>
@@ -1639,7 +1794,23 @@
         <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -1660,200 +1831,200 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" t="s">
         <v>45</v>
       </c>
-      <c r="B17" t="s">
-        <v>46</v>
-      </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" t="s">
         <v>47</v>
       </c>
-      <c r="B18" t="s">
-        <v>48</v>
-      </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1874,68 +2045,68 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" t="s">
         <v>72</v>
       </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1956,145 +2127,145 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2115,156 +2286,156 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2283,123 +2454,249 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" t="s">
         <v>139</v>
       </c>
-      <c r="B2" t="s">
-        <v>140</v>
-      </c>
       <c r="C2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B4" t="s">
         <v>142</v>
       </c>
-      <c r="B4" t="s">
-        <v>143</v>
-      </c>
       <c r="C4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" t="s">
         <v>145</v>
       </c>
-      <c r="B6" t="s">
-        <v>146</v>
-      </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" t="s">
         <v>151</v>
       </c>
-      <c r="B11" t="s">
-        <v>152</v>
-      </c>
       <c r="C11" t="s">
-        <v>161</v>
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A613073-A773-4746-A729-80D6720B18AF}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/data/Quarto_YAMLs.xlsx
+++ b/data/Quarto_YAMLs.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R入門\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A749EB1A-C386-4946-AE8B-B8731214CE64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB3F771-3A99-49C8-A560-2A23D712C947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19230" yWindow="2880" windowWidth="20775" windowHeight="11835" activeTab="7" xr2:uid="{BD8A1D6D-0391-4D96-8986-F577B78F0501}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="16440" activeTab="7" xr2:uid="{BD8A1D6D-0391-4D96-8986-F577B78F0501}"/>
   </bookViews>
   <sheets>
     <sheet name="format" sheetId="1" r:id="rId1"/>
@@ -1753,6 +1748,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1816,6 +1812,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2030,6 +2027,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2112,6 +2110,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2271,6 +2270,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2441,6 +2441,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2576,6 +2577,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2702,5 +2704,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>